--- a/data/member_info.xlsx
+++ b/data/member_info.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>full_name</t>
   </si>
@@ -83,10 +83,7 @@
     <t>刘金龙</t>
   </si>
   <si>
-    <t>IEf1pIVCeeIqGfSuie1OmjB+liujinlong@noreply.cnb.cool</t>
-  </si>
-  <si>
-    <t>2272756717@qq.com</t>
+    <t>jinlong.liu@clife.cn</t>
   </si>
   <si>
     <t>曾小芬</t>
@@ -107,9 +104,6 @@
     <t>xin.wang@clife.cn</t>
   </si>
   <si>
-    <t>gavinwangxin@163.com</t>
-  </si>
-  <si>
     <t>叶小凤</t>
   </si>
   <si>
@@ -128,22 +122,16 @@
     <t>jing.wang@clife.cn</t>
   </si>
   <si>
-    <t>JwJZtwBUAhUdLXbYfRB8eG+cnb.bAIKUfhtAOA@noreply.cnb.cool</t>
-  </si>
-  <si>
     <t>龚欣柔</t>
   </si>
   <si>
-    <t>feuWo8Sxfs9e90CpeO9FE1A+gongxinrou@noreply.cnb.cool</t>
+    <t>xinrou.gong@clife.cn</t>
   </si>
   <si>
     <t>黄亚康</t>
   </si>
   <si>
     <t>yakang.huang@clife.cn</t>
-  </si>
-  <si>
-    <t>K0SZNCdweTMle0fL3WbCOV+cnb.ZcZGQmrpQGA@noreply.cnb.cool</t>
   </si>
   <si>
     <t>龚航</t>
@@ -1200,7 +1188,7 @@
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2"/>
@@ -1209,128 +1197,124 @@
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B9" r:id="rId1" display="jinlong.liu@clife.cn"/>
+    <hyperlink ref="B16" r:id="rId2" display="xinrou.gong@clife.cn"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/member_info.xlsx
+++ b/data/member_info.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="432"/>
+    <workbookView windowHeight="17775" tabRatio="432"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>full_name</t>
   </si>
@@ -35,21 +35,12 @@
     <t>email1</t>
   </si>
   <si>
-    <t>email2</t>
-  </si>
-  <si>
     <t>乐天</t>
   </si>
   <si>
     <t>tian.le@clife.cn</t>
   </si>
   <si>
-    <t>宋智刚</t>
-  </si>
-  <si>
-    <t>zhigang.song@clife.cn</t>
-  </si>
-  <si>
     <t>庄允贵</t>
   </si>
   <si>
@@ -122,12 +113,6 @@
     <t>jing.wang@clife.cn</t>
   </si>
   <si>
-    <t>龚欣柔</t>
-  </si>
-  <si>
-    <t>xinrou.gong@clife.cn</t>
-  </si>
-  <si>
     <t>黄亚康</t>
   </si>
   <si>
@@ -144,12 +129,6 @@
   </si>
   <si>
     <t>zhuowen.huang@clife.cn</t>
-  </si>
-  <si>
-    <t>马可一</t>
-  </si>
-  <si>
-    <t>keyi.ma@clife.cn</t>
   </si>
   <si>
     <t>刘臣</t>
@@ -1100,220 +1079,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
     <col min="2" max="2" width="81.5" customWidth="1"/>
-    <col min="3" max="3" width="76.125" customWidth="1"/>
-    <col min="5" max="5" width="75" customWidth="1"/>
-    <col min="6" max="6" width="19.375" customWidth="1"/>
-    <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="15.5" customWidth="1"/>
-    <col min="11" max="14" width="12.875"/>
-    <col min="15" max="15" width="11.625"/>
-    <col min="20" max="21" width="11.625"/>
-    <col min="22" max="22" width="9.25"/>
-    <col min="29" max="30" width="9.25"/>
-    <col min="31" max="31" width="12.875"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="9" max="12" width="12.875"/>
+    <col min="13" max="13" width="11.625"/>
+    <col min="18" max="19" width="11.625"/>
+    <col min="20" max="20" width="9.25"/>
+    <col min="27" max="28" width="9.25"/>
+    <col min="29" max="29" width="12.875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" display="jinlong.liu@clife.cn"/>
-    <hyperlink ref="B16" r:id="rId2" display="xinrou.gong@clife.cn"/>
+    <hyperlink ref="B8" r:id="rId1" display="jinlong.liu@clife.cn"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
